--- a/Dataset - Daily Caffeine Consumption and Lecture Concentration.xlsx
+++ b/Dataset - Daily Caffeine Consumption and Lecture Concentration.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucaswang/Desktop/STA304/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C63472-DA49-3843-9416-DF17084C689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4A9FDB-EF82-FE4C-91AC-201E3AA328AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="3160" windowWidth="29760" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12580" yWindow="3140" windowWidth="26740" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>studentID</t>
   </si>
@@ -245,6 +258,9 @@
   </si>
   <si>
     <t>Lecture_attended</t>
+  </si>
+  <si>
+    <t>Caffeine_consumption</t>
   </si>
 </sst>
 </file>
@@ -300,18 +316,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -375,10 +411,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -393,14 +429,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:J66" headerRowDxfId="0">
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:K66" headerRowDxfId="1">
+  <tableColumns count="11">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="studentID"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Section"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coffee"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tea"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Energy_drink"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Other_beverage"/>
+    <tableColumn id="12" xr3:uid="{C75633E5-F06C-6044-8C85-DD1462A474B1}" name="Caffeine_consumption" dataDxfId="0">
+      <calculatedColumnFormula>SUM(C2, D2, E2, F2)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Concentration"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Sleeping_hour"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Stress_level"/>
@@ -611,7 +650,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
@@ -620,14 +659,15 @@
     <col min="4" max="4" width="6.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="16" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="17" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -646,20 +686,23 @@
       <c r="F1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -679,19 +722,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>8</v>
+        <f t="shared" ref="G2:G33" si="0">SUM(C2, D2, E2, F2)</f>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1">
         <v>7.5</v>
       </c>
-      <c r="I2" s="1">
-        <v>3</v>
-      </c>
       <c r="J2" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+      <c r="K2" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -711,19 +758,23 @@
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="H3" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I3" s="1">
         <v>7</v>
       </c>
       <c r="J3" s="1">
+        <v>7</v>
+      </c>
+      <c r="K3" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -743,19 +794,23 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K4" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,19 +830,23 @@
         <v>0</v>
       </c>
       <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
         <v>10</v>
       </c>
-      <c r="H5" s="1">
-        <v>6</v>
-      </c>
       <c r="I5" s="1">
         <v>6</v>
       </c>
       <c r="J5" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+      <c r="K5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,19 +866,23 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" s="1">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1">
         <v>10</v>
       </c>
-      <c r="J6" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K6" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,19 +902,23 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H7" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J7" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -871,19 +938,23 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="H8" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,19 +974,23 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="H9" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -935,19 +1010,23 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J10" s="1">
+        <v>5</v>
+      </c>
+      <c r="K10" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -967,19 +1046,23 @@
         <v>0.8</v>
       </c>
       <c r="G11" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>2.8</v>
       </c>
       <c r="H11" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I11" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -999,19 +1082,23 @@
         <v>1.5</v>
       </c>
       <c r="G12" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
       <c r="H12" s="1">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1">
         <v>7.71</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
       <c r="J12" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1031,19 +1118,23 @@
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H13" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="1">
         <v>7</v>
       </c>
       <c r="J13" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="K13" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1063,19 +1154,23 @@
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H14" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" s="1">
+        <v>7</v>
+      </c>
+      <c r="K14" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,19 +1190,23 @@
         <v>0</v>
       </c>
       <c r="G15" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
         <v>6.5</v>
       </c>
-      <c r="I15" s="1">
-        <v>7</v>
-      </c>
       <c r="J15" s="1">
+        <v>7</v>
+      </c>
+      <c r="K15" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1127,19 +1226,23 @@
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
+        <v>8</v>
+      </c>
+      <c r="I16" s="1">
         <v>7.5</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>4</v>
       </c>
-      <c r="J16" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K16" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1159,19 +1262,23 @@
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="H17" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I17" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17" s="1">
+        <v>3</v>
+      </c>
+      <c r="K17" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1191,19 +1298,23 @@
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H18" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1">
         <v>8</v>
       </c>
       <c r="J18" s="1">
+        <v>8</v>
+      </c>
+      <c r="K18" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1223,19 +1334,23 @@
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K19" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1255,19 +1370,23 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H20" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1">
+        <v>7</v>
+      </c>
+      <c r="J20" s="1">
         <v>4</v>
       </c>
-      <c r="J20" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1287,19 +1406,23 @@
         <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="H21" s="1">
+        <v>6</v>
+      </c>
+      <c r="I21" s="1">
         <v>7.5</v>
-      </c>
-      <c r="I21" s="1">
-        <v>4</v>
       </c>
       <c r="J21" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K21" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,19 +1442,23 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="K22" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1351,19 +1478,23 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H23" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I23" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J23" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1383,19 +1514,23 @@
         <v>1.4</v>
       </c>
       <c r="G24" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>2.8</v>
       </c>
       <c r="H24" s="1">
         <v>8</v>
       </c>
       <c r="I24" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J24" s="1">
+        <v>5</v>
+      </c>
+      <c r="K24" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -1415,19 +1550,23 @@
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>4.29</v>
       </c>
       <c r="H25" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J25" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K25" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1447,19 +1586,23 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H26" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I26" s="1">
         <v>8</v>
       </c>
       <c r="J26" s="1">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1479,19 +1622,23 @@
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="H27" s="1">
+        <v>7</v>
+      </c>
+      <c r="I27" s="1">
         <v>5.5</v>
       </c>
-      <c r="I27" s="1">
-        <v>8</v>
-      </c>
       <c r="J27" s="1">
+        <v>8</v>
+      </c>
+      <c r="K27" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1511,19 +1658,23 @@
         <v>7</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="H28" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I28" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J28" s="1">
+        <v>3</v>
+      </c>
+      <c r="K28" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1543,19 +1694,23 @@
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="H29" s="1">
+        <v>8</v>
+      </c>
+      <c r="I29" s="1">
         <v>6.5</v>
       </c>
-      <c r="I29" s="1">
-        <v>7</v>
-      </c>
       <c r="J29" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="K29" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1575,19 +1730,23 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="H30" s="1">
         <v>7</v>
       </c>
       <c r="I30" s="1">
+        <v>7</v>
+      </c>
+      <c r="J30" s="1">
         <v>9</v>
       </c>
-      <c r="J30" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1607,19 +1766,23 @@
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
+        <v>7</v>
+      </c>
+      <c r="I31" s="1">
         <v>7.25</v>
       </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
       <c r="J31" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -1639,19 +1802,23 @@
         <v>0</v>
       </c>
       <c r="G32" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
         <v>10</v>
       </c>
-      <c r="H32" s="1">
-        <v>8</v>
-      </c>
       <c r="I32" s="1">
         <v>8</v>
       </c>
       <c r="J32" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+      <c r="K32" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -1671,19 +1838,23 @@
         <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="H33" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+      <c r="K33" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,19 +1874,23 @@
         <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>5</v>
+        <f t="shared" ref="G34:G65" si="1">SUM(C34, D34, E34, F34)</f>
+        <v>12</v>
       </c>
       <c r="H34" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J34" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K34" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -1735,19 +1910,23 @@
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
+        <v>8</v>
+      </c>
+      <c r="I35" s="1">
         <v>9</v>
       </c>
-      <c r="I35" s="1">
-        <v>5</v>
-      </c>
       <c r="J35" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K35" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -1767,19 +1946,23 @@
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="1">
+        <v>5</v>
+      </c>
+      <c r="K36" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1799,19 +1982,23 @@
         <v>1</v>
       </c>
       <c r="G37" s="1">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="H37" s="1">
         <v>10</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>9</v>
       </c>
-      <c r="I37" s="1">
-        <v>8</v>
-      </c>
       <c r="J37" s="1">
+        <v>8</v>
+      </c>
+      <c r="K37" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -1831,19 +2018,23 @@
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I38" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J38" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K38" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1863,19 +2054,23 @@
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H39" s="1">
+        <v>8</v>
+      </c>
+      <c r="I39" s="1">
         <v>9</v>
       </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
       <c r="J39" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K39" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1895,7 +2090,8 @@
         <v>10</v>
       </c>
       <c r="G40" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="H40" s="1">
         <v>8</v>
@@ -1904,10 +2100,13 @@
         <v>8</v>
       </c>
       <c r="J40" s="1">
+        <v>8</v>
+      </c>
+      <c r="K40" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -1927,19 +2126,23 @@
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H41" s="1">
         <v>8</v>
       </c>
       <c r="I41" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J41" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="K41" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -1959,19 +2162,23 @@
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H42" s="1">
         <v>7</v>
       </c>
       <c r="I42" s="1">
+        <v>7</v>
+      </c>
+      <c r="J42" s="1">
         <v>4</v>
       </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -1991,19 +2198,23 @@
         <v>0</v>
       </c>
       <c r="G43" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H43" s="1">
         <v>9</v>
       </c>
-      <c r="H43" s="1">
-        <v>7</v>
-      </c>
       <c r="I43" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J43" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K43" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -2023,19 +2234,23 @@
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H44" s="1">
         <v>7</v>
       </c>
       <c r="I44" s="1">
+        <v>7</v>
+      </c>
+      <c r="J44" s="1">
         <v>4</v>
       </c>
-      <c r="J44" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K44" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
@@ -2055,10 +2270,11 @@
         <v>0</v>
       </c>
       <c r="G45" s="1">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="H45" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I45" s="1">
         <v>7</v>
@@ -2066,8 +2282,11 @@
       <c r="J45" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K45" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -2087,19 +2306,23 @@
         <v>5</v>
       </c>
       <c r="G46" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H46" s="1">
         <v>4</v>
       </c>
-      <c r="H46" s="1">
-        <v>7</v>
-      </c>
       <c r="I46" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J46" s="1">
+        <v>5</v>
+      </c>
+      <c r="K46" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -2119,19 +2342,23 @@
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
+        <v>5</v>
+      </c>
+      <c r="I47" s="1">
         <v>10</v>
       </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
       <c r="J47" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K47" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
@@ -2151,19 +2378,23 @@
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H48" s="1">
         <v>8</v>
       </c>
       <c r="I48" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J48" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K48" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
@@ -2183,19 +2414,23 @@
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H49" s="1">
+        <v>5</v>
+      </c>
+      <c r="I49" s="1">
         <v>9</v>
       </c>
-      <c r="I49" s="1">
-        <v>5</v>
-      </c>
       <c r="J49" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K49" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
@@ -2215,19 +2450,23 @@
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H50" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I50" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J50" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+      <c r="K50" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -2247,19 +2486,23 @@
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I51" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J51" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="K51" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -2279,19 +2522,23 @@
         <v>2</v>
       </c>
       <c r="G52" s="1">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="H52" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I52" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
@@ -2309,19 +2556,23 @@
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I53" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K53" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
@@ -2341,19 +2592,23 @@
         <v>3</v>
       </c>
       <c r="G54" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="H54" s="1">
         <v>9</v>
       </c>
-      <c r="H54" s="1">
-        <v>6</v>
-      </c>
       <c r="I54" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J54" s="1">
+        <v>8</v>
+      </c>
+      <c r="K54" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -2373,19 +2628,23 @@
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H55" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I55" s="1">
         <v>7</v>
       </c>
       <c r="J55" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="K55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
@@ -2405,19 +2664,23 @@
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H56" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I56" s="1">
+        <v>8</v>
+      </c>
+      <c r="J56" s="1">
         <v>4</v>
       </c>
-      <c r="J56" s="1">
+      <c r="K56" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
@@ -2437,19 +2700,23 @@
         <v>1</v>
       </c>
       <c r="G57" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H57" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I57" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J57" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K57" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
@@ -2469,19 +2736,23 @@
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H58" s="1">
         <v>6</v>
       </c>
       <c r="I58" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J58" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="K58" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
@@ -2501,19 +2772,23 @@
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>1.9</v>
       </c>
       <c r="H59" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I59" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J59" s="1">
+        <v>7</v>
+      </c>
+      <c r="K59" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
@@ -2529,20 +2804,24 @@
       <c r="E60" s="1">
         <v>0</v>
       </c>
-      <c r="G60" s="1">
-        <v>1</v>
+      <c r="G60">
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H60" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I60" s="1">
         <v>9</v>
       </c>
       <c r="J60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+      <c r="K60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
@@ -2562,19 +2841,23 @@
         <v>0</v>
       </c>
       <c r="G61" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
         <v>9</v>
       </c>
-      <c r="H61" s="1">
-        <v>6</v>
-      </c>
       <c r="I61" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J61" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+      <c r="K61" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
@@ -2594,19 +2877,23 @@
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H62" s="1">
+        <v>6</v>
+      </c>
+      <c r="I62" s="1">
         <v>7.5</v>
       </c>
-      <c r="I62" s="1">
+      <c r="J62" s="1">
         <v>4</v>
       </c>
-      <c r="J62" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K62" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
@@ -2626,19 +2913,23 @@
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
+        <v>7</v>
+      </c>
+      <c r="I63" s="1">
         <v>11</v>
       </c>
-      <c r="I63" s="1">
+      <c r="J63" s="1">
         <v>10</v>
       </c>
-      <c r="J63" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K63" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
@@ -2658,19 +2949,23 @@
         <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="H64" s="1">
+        <v>3</v>
+      </c>
+      <c r="I64" s="1">
         <v>6.5</v>
       </c>
-      <c r="I64" s="1">
-        <v>6</v>
-      </c>
       <c r="J64" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+      <c r="K64" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
@@ -2690,19 +2985,23 @@
         <v>10</v>
       </c>
       <c r="G65" s="1">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="H65" s="1">
+        <v>5</v>
+      </c>
+      <c r="I65" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="I65" s="1">
-        <v>6</v>
-      </c>
       <c r="J65" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K65" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
@@ -2722,15 +3021,19 @@
         <v>2</v>
       </c>
       <c r="G66" s="1">
-        <v>8</v>
+        <f t="shared" ref="G66:G97" si="2">SUM(C66, D66, E66, F66)</f>
+        <v>9</v>
       </c>
       <c r="H66" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I66" s="1">
         <v>6</v>
       </c>
       <c r="J66" s="1">
+        <v>6</v>
+      </c>
+      <c r="K66" s="1">
         <v>4</v>
       </c>
     </row>

--- a/Dataset - Daily Caffeine Consumption and Lecture Concentration.xlsx
+++ b/Dataset - Daily Caffeine Consumption and Lecture Concentration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucaswang/Desktop/STA304/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4A9FDB-EF82-FE4C-91AC-201E3AA328AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB5663B-364D-0D46-9A98-FD359FF7BD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12580" yWindow="3140" windowWidth="26740" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7460" yWindow="3140" windowWidth="26740" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>studentID</t>
   </si>
@@ -177,9 +177,6 @@
   </si>
   <si>
     <t>LaTexSupremacy11</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/forms/d/e/1FAIpQLSeA6EAI8MAVNOU3EEXFpD7ZBhiIcfiocILYZzYOcAoAn8vuJQ/viewform</t>
   </si>
   <si>
     <t>wwUs</t>
@@ -267,7 +264,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -280,12 +277,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="2">
@@ -308,12 +299,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -429,7 +417,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:K66" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:K65" headerRowDxfId="1">
   <tableColumns count="11">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="studentID"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Section"/>
@@ -650,7 +638,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
@@ -667,39 +655,39 @@
     <col min="12" max="17" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1874,7 +1862,7 @@
         <v>4</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" ref="G34:G65" si="1">SUM(C34, D34, E34, F34)</f>
+        <f t="shared" ref="G34:G64" si="1">SUM(C34, D34, E34, F34)</f>
         <v>12</v>
       </c>
       <c r="H34" s="1">
@@ -2395,14 +2383,14 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -2415,19 +2403,19 @@
       </c>
       <c r="G49" s="1">
         <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H49" s="1">
+        <v>6</v>
+      </c>
+      <c r="I49" s="1">
+        <v>7</v>
+      </c>
+      <c r="J49" s="1">
         <v>3</v>
       </c>
-      <c r="H49" s="1">
-        <v>5</v>
-      </c>
-      <c r="I49" s="1">
-        <v>9</v>
-      </c>
-      <c r="J49" s="1">
-        <v>5</v>
-      </c>
       <c r="K49" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2435,10 +2423,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -2451,19 +2439,19 @@
       </c>
       <c r="G50" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I50" s="1">
         <v>7</v>
       </c>
       <c r="J50" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K50" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2471,65 +2459,63 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H51" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I51" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="1">
-        <v>2</v>
-      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
       </c>
       <c r="F52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
@@ -2542,34 +2528,36 @@
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1"/>
+      <c r="B53" s="1">
+        <v>2</v>
+      </c>
       <c r="C53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
       </c>
       <c r="F53" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H53" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I53" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J53" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K53" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2580,32 +2568,32 @@
         <v>2</v>
       </c>
       <c r="C54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
       </c>
       <c r="F54" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H54" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I54" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K54" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2613,10 +2601,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -2629,19 +2617,19 @@
       </c>
       <c r="G55" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I55" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J55" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K55" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2649,23 +2637,23 @@
         <v>55</v>
       </c>
       <c r="B56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56" s="1">
         <v>6</v>
@@ -2674,10 +2662,10 @@
         <v>8</v>
       </c>
       <c r="J56" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K56" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2685,7 +2673,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" s="1">
         <v>0</v>
@@ -2694,26 +2682,26 @@
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
         <v>6</v>
       </c>
       <c r="I57" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J57" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K57" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2721,10 +2709,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" s="1">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
@@ -2737,10 +2725,10 @@
       </c>
       <c r="G58" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H58" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I58" s="1">
         <v>6</v>
@@ -2749,7 +2737,7 @@
         <v>7</v>
       </c>
       <c r="K58" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2757,35 +2745,32 @@
         <v>58</v>
       </c>
       <c r="B59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" s="1">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
+      <c r="G59">
         <f t="shared" si="1"/>
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="H59" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J59" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K59" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2796,29 +2781,32 @@
         <v>1</v>
       </c>
       <c r="C60" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
-      <c r="G60">
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>9</v>
+      </c>
+      <c r="I60" s="1">
+        <v>6</v>
+      </c>
+      <c r="J60" s="1">
         <v>3</v>
       </c>
-      <c r="H60" s="1">
-        <v>1</v>
-      </c>
-      <c r="I60" s="1">
-        <v>9</v>
-      </c>
-      <c r="J60" s="1">
-        <v>9</v>
-      </c>
       <c r="K60" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2826,10 +2814,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
@@ -2842,19 +2830,19 @@
       </c>
       <c r="G61" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I61" s="1">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J61" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2865,7 +2853,7 @@
         <v>2</v>
       </c>
       <c r="C62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -2878,19 +2866,19 @@
       </c>
       <c r="G62" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="1">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="J62" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K62" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2898,35 +2886,35 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H63" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I63" s="1">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="J63" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K63" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2934,35 +2922,35 @@
         <v>63</v>
       </c>
       <c r="B64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G64" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H64" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I64" s="1">
-        <v>6.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J64" s="1">
         <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2970,81 +2958,42 @@
         <v>64</v>
       </c>
       <c r="B65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E65" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G65" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f t="shared" ref="G65" si="2">SUM(C65, D65, E65, F65)</f>
+        <v>9</v>
       </c>
       <c r="H65" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I65" s="1">
-        <v>8.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="J65" s="1">
         <v>6</v>
       </c>
       <c r="K65" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1</v>
-      </c>
-      <c r="C66" s="1">
-        <v>2</v>
-      </c>
-      <c r="D66" s="1">
-        <v>2</v>
-      </c>
-      <c r="E66" s="1">
-        <v>3</v>
-      </c>
-      <c r="F66" s="1">
-        <v>2</v>
-      </c>
-      <c r="G66" s="1">
-        <f t="shared" ref="G66:G97" si="2">SUM(C66, D66, E66, F66)</f>
-        <v>9</v>
-      </c>
-      <c r="H66" s="1">
-        <v>8</v>
-      </c>
-      <c r="I66" s="1">
-        <v>6</v>
-      </c>
-      <c r="J66" s="1">
-        <v>6</v>
-      </c>
-      <c r="K66" s="1">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A49" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Dataset - Daily Caffeine Consumption and Lecture Concentration.xlsx
+++ b/Dataset - Daily Caffeine Consumption and Lecture Concentration.xlsx
@@ -248,8 +248,8 @@
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -268,6 +268,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
@@ -275,7 +290,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,7 +312,55 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,78 +374,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -389,22 +390,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -412,7 +412,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,7 +427,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,7 +487,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,163 +601,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -630,17 +630,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,36 +655,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -712,157 +686,183 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -973,7 +973,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="D4346F555FFF6A132FB8DB6A32AA8985">
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="5855F0856EFC96C2F6B8DB6A7226DE50">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
@@ -3059,7 +3059,9 @@
       <c r="A52" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="4"/>
+      <c r="B52" s="4">
+        <v>1</v>
+      </c>
       <c r="C52" s="4">
         <v>0</v>
       </c>
